--- a/Outputs/Scenarios/PtX_demand_HR_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_HR_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0006628818471006026</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0007148512001163051</v>
+        <v>0.0008147123759139894</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001191418666860509</v>
+        <v>0.001097687470464919</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>9.55100534594075e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0004765674667442035</v>
+        <v>0.0004704374873421084</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.000981315871154448</v>
       </c>
       <c r="K30" t="n">
-        <v>0.003844949908377435</v>
+        <v>0.004382070386976756</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.006408249847295725</v>
+        <v>0.005904100515330285</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>5.164820374497096e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.00256329993891829</v>
+        <v>0.002530328792284408</v>
       </c>
     </row>
     <row r="43">
